--- a/apps/worker/samples/서류 분류 코드표.xlsx
+++ b/apps/worker/samples/서류 분류 코드표.xlsx
@@ -7,14 +7,14 @@
     <sheet sheetId="1" name="분류코드" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'분류코드'!$A1:$D67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'분류코드'!$A1:$D68</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="151">
   <si>
     <t>2차 분류 (중분류)</t>
   </si>
@@ -230,9 +230,6 @@
   </si>
   <si>
     <t>VE 원가절감</t>
-  </si>
-  <si>
-    <t>311</t>
   </si>
   <si>
     <t>본사 공지사항</t>
@@ -887,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1246,364 +1243,374 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="4" t="s">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C36" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="4" t="s">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C44" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D44" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="4" t="s">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="3" t="s">
+      <c r="D45" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="4" t="s">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C46" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="4" t="s">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C56" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D56" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C68" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="D68" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1614,16 +1621,16 @@
     <mergeCell ref="B3:B14"/>
     <mergeCell ref="A15:A23"/>
     <mergeCell ref="B15:B23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="B24:B34"/>
-    <mergeCell ref="A35:A42"/>
-    <mergeCell ref="B35:B42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A45:A54"/>
-    <mergeCell ref="B45:B54"/>
-    <mergeCell ref="A55:A65"/>
-    <mergeCell ref="B55:B65"/>
+    <mergeCell ref="A24:A35"/>
+    <mergeCell ref="B24:B35"/>
+    <mergeCell ref="A36:A43"/>
+    <mergeCell ref="B36:B43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A46:A55"/>
+    <mergeCell ref="B46:B55"/>
+    <mergeCell ref="A56:A66"/>
+    <mergeCell ref="B56:B66"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/apps/worker/samples/서류 분류 코드표.xlsx
+++ b/apps/worker/samples/서류 분류 코드표.xlsx
@@ -7,14 +7,14 @@
     <sheet sheetId="1" name="분류코드" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'분류코드'!$A1:$D68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'분류코드'!$A1:$D67</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="152">
   <si>
     <t>2차 분류 (중분류)</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>VE 원가절감</t>
+  </si>
+  <si>
+    <t>311</t>
   </si>
   <si>
     <t>본사 공지사항</t>
@@ -884,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1243,374 +1246,364 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="3" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
+      <c r="A35" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="C35" s="3" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>74</v>
-      </c>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
       <c r="C36" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
+      <c r="A43" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="C43" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
       <c r="C44" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
+      <c r="A45" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="C45" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>98</v>
-      </c>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
       <c r="C46" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
+      <c r="A55" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="C55" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>120</v>
-      </c>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
       <c r="C56" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
+      <c r="A66" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="C66" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1621,16 +1614,16 @@
     <mergeCell ref="B3:B14"/>
     <mergeCell ref="A15:A23"/>
     <mergeCell ref="B15:B23"/>
-    <mergeCell ref="A24:A35"/>
-    <mergeCell ref="B24:B35"/>
-    <mergeCell ref="A36:A43"/>
-    <mergeCell ref="B36:B43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A46:A55"/>
-    <mergeCell ref="B46:B55"/>
-    <mergeCell ref="A56:A66"/>
-    <mergeCell ref="B56:B66"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="B24:B34"/>
+    <mergeCell ref="A35:A42"/>
+    <mergeCell ref="B35:B42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A45:A54"/>
+    <mergeCell ref="B45:B54"/>
+    <mergeCell ref="A55:A65"/>
+    <mergeCell ref="B55:B65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/apps/worker/samples/서류 분류 코드표.xlsx
+++ b/apps/worker/samples/서류 분류 코드표.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="분류코드" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="공무관련" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'분류코드'!$A1:$D67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'공무관련'!$A1:$D67</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>

--- a/apps/worker/samples/서류 분류 코드표.xlsx
+++ b/apps/worker/samples/서류 분류 코드표.xlsx
@@ -893,7 +893,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
